--- a/output/isabel-cohorts/이서연반_시험수준별_성적.xlsx
+++ b/output/isabel-cohorts/이서연반_시험수준별_성적.xlsx
@@ -22,8 +22,410 @@
 </workbook>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">듣기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">독해 개수 기록 없음</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="49">
   <si>
     <r>
       <rPr>
@@ -101,7 +503,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -206,6 +608,25 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">서예준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이시원</t>
     </r>
     <r>
       <rPr>
@@ -342,7 +763,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1(2025) 1</t>
+      <t xml:space="preserve">1(2025) 1·2·3·4</t>
     </r>
     <r>
       <rPr>
@@ -798,49 +1219,49 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">· 2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년 중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">차 성적만 받았습니다</t>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 1·2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차는 총점만 기록된 학생이 있어 듣기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">독해 칸이 비어 있습니다</t>
     </r>
     <r>
       <rPr>
@@ -936,7 +1357,24 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">고</t>
+      <t xml:space="preserve">이서연 반은 현재 중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라 고</t>
     </r>
     <r>
       <rPr>
@@ -953,7 +1391,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">모의고사는 아직 보지 않아 시트가 없습니다</t>
+      <t xml:space="preserve">모의고사는 아직 보지 않았습니다</t>
     </r>
     <r>
       <rPr>
@@ -974,23 +1412,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이시원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -1323,7 +1744,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1(2025) 1</t>
+      <t xml:space="preserve">1(2025) 1·2·3·4</t>
     </r>
     <r>
       <rPr>
@@ -1568,6 +1989,156 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차
+고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모의고사</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차
+고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모의고사</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차
+고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모의고사</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 4</t>
     </r>
     <r>
       <rPr>
@@ -1721,6 +2292,9 @@
     <t xml:space="preserve">서예준</t>
   </si>
   <si>
+    <t xml:space="preserve">이시원</t>
+  </si>
+  <si>
     <t xml:space="preserve">반 평균</t>
   </si>
   <si>
@@ -2076,7 +2650,7 @@
     <numFmt numFmtId="166" formatCode="\+0.0;\-0.0;0.0"/>
     <numFmt numFmtId="167" formatCode="\+0;\-0;0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2162,6 +2736,16 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -2383,7 +2967,7 @@
       <rgbColor rgb="FF46AAC4"/>
       <rgbColor rgb="FF98B855"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFF59240"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF7D5FA0"/>
       <rgbColor rgb="FF969696"/>
@@ -2505,18 +3089,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$5:$D$5</c:f>
+              <c:f>'고1 모의고사'!$B$5:$G$5</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -2525,17 +3121,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$6:$D$6</c:f>
+              <c:f>'고1 모의고사'!$B$6:$G$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>66</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>75</c:v>
                 </c:pt>
               </c:numCache>
@@ -2604,18 +3209,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$5:$D$5</c:f>
+              <c:f>'고1 모의고사'!$B$5:$G$5</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -2624,17 +3241,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$7:$D$7</c:f>
+              <c:f>'고1 모의고사'!$B$7:$G$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>87</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>73</c:v>
                 </c:pt>
               </c:numCache>
@@ -2703,18 +3329,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$5:$D$5</c:f>
+              <c:f>'고1 모의고사'!$B$5:$G$5</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -2723,17 +3361,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$8:$D$8</c:f>
+              <c:f>'고1 모의고사'!$B$8:$G$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>87</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
@@ -2802,18 +3449,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$5:$D$5</c:f>
+              <c:f>'고1 모의고사'!$B$5:$G$5</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -2822,17 +3481,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$9:$D$9</c:f>
+              <c:f>'고1 모의고사'!$B$9:$G$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>88</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>74</c:v>
                 </c:pt>
               </c:numCache>
@@ -2901,18 +3569,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$5:$D$5</c:f>
+              <c:f>'고1 모의고사'!$B$5:$G$5</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -2921,18 +3601,147 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$10:$D$10</c:f>
+              <c:f>'고1 모의고사'!$B$10:$G$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>73</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>82</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고1 모의고사'!A11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이시원</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="f59240"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고1 모의고사'!$B$5:$G$5</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>중1 1차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
                 <c:pt idx="2">
-                  <c:v>82</c:v>
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>중2 1차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>중2 2차
+고1 모의고사</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고1 모의고사'!$B$11:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2947,11 +3756,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="58861202"/>
-        <c:axId val="28967038"/>
+        <c:axId val="32900627"/>
+        <c:axId val="21361670"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="58861202"/>
+        <c:axId val="32900627"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2983,7 +3792,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28967038"/>
+        <c:crossAx val="21361670"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2991,7 +3800,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28967038"/>
+        <c:axId val="21361670"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3069,7 +3878,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58861202"/>
+        <c:crossAx val="32900627"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -3171,7 +3980,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A15</c:f>
+              <c:f>'고1 모의고사'!A16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3227,18 +4036,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$14:$D$14</c:f>
+              <c:f>'고1 모의고사'!$B$15:$G$15</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -3247,17 +4068,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$15:$D$15</c:f>
+              <c:f>'고1 모의고사'!$B$16:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
@@ -3270,7 +4097,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A16</c:f>
+              <c:f>'고1 모의고사'!A17</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3326,18 +4153,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$14:$D$14</c:f>
+              <c:f>'고1 모의고사'!$B$15:$G$15</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -3346,17 +4185,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$16:$D$16</c:f>
+              <c:f>'고1 모의고사'!$B$17:$G$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
@@ -3369,7 +4214,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A17</c:f>
+              <c:f>'고1 모의고사'!A18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3425,18 +4270,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$14:$D$14</c:f>
+              <c:f>'고1 모의고사'!$B$15:$G$15</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -3445,17 +4302,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$17:$D$17</c:f>
+              <c:f>'고1 모의고사'!$B$18:$G$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
@@ -3468,7 +4331,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A18</c:f>
+              <c:f>'고1 모의고사'!A19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3524,18 +4387,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$14:$D$14</c:f>
+              <c:f>'고1 모의고사'!$B$15:$G$15</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -3544,17 +4419,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$18:$D$18</c:f>
+              <c:f>'고1 모의고사'!$B$19:$G$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
@@ -3567,7 +4448,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A19</c:f>
+              <c:f>'고1 모의고사'!A20</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3623,18 +4504,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$14:$D$14</c:f>
+              <c:f>'고1 모의고사'!$B$15:$G$15</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -3643,18 +4536,138 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$19:$D$19</c:f>
+              <c:f>'고1 모의고사'!$B$20:$G$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>16</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고1 모의고사'!A21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이시원</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="f59240"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고1 모의고사'!$B$15:$G$15</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>중1 1차
+고1 모의고사</c:v>
+                </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>중2 1차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>중2 2차
+고1 모의고사</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고1 모의고사'!$B$21:$G$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3669,11 +4682,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="88213278"/>
-        <c:axId val="48075547"/>
+        <c:axId val="42062392"/>
+        <c:axId val="50354999"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="88213278"/>
+        <c:axId val="42062392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3705,7 +4718,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48075547"/>
+        <c:crossAx val="50354999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3713,7 +4726,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48075547"/>
+        <c:axId val="50354999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -3791,7 +4804,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88213278"/>
+        <c:crossAx val="42062392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -3893,7 +4906,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A24</c:f>
+              <c:f>'고1 모의고사'!A26</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3949,18 +4962,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$23:$D$23</c:f>
+              <c:f>'고1 모의고사'!$B$25:$G$25</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -3969,17 +4994,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$24:$D$24</c:f>
+              <c:f>'고1 모의고사'!$B$26:$G$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
@@ -3992,7 +5023,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A25</c:f>
+              <c:f>'고1 모의고사'!A27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4048,18 +5079,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$23:$D$23</c:f>
+              <c:f>'고1 모의고사'!$B$25:$G$25</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -4068,17 +5111,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$25:$D$25</c:f>
+              <c:f>'고1 모의고사'!$B$27:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>23</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
@@ -4091,7 +5140,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A26</c:f>
+              <c:f>'고1 모의고사'!A28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4147,18 +5196,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$23:$D$23</c:f>
+              <c:f>'고1 모의고사'!$B$25:$G$25</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -4167,17 +5228,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$26:$D$26</c:f>
+              <c:f>'고1 모의고사'!$B$28:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>23</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>23</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>28</c:v>
                 </c:pt>
               </c:numCache>
@@ -4190,7 +5257,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A27</c:f>
+              <c:f>'고1 모의고사'!A29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4246,18 +5313,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$23:$D$23</c:f>
+              <c:f>'고1 모의고사'!$B$25:$G$25</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -4266,17 +5345,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$27:$D$27</c:f>
+              <c:f>'고1 모의고사'!$B$29:$G$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
@@ -4289,7 +5374,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고1 모의고사'!A28</c:f>
+              <c:f>'고1 모의고사'!A30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4345,18 +5430,30 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고1 모의고사'!$B$23:$D$23</c:f>
+              <c:f>'고1 모의고사'!$B$25:$G$25</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1 모의고사</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1 모의고사</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1 모의고사</c:v>
                 </c:pt>
@@ -4365,18 +5462,138 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고1 모의고사'!$B$28:$D$28</c:f>
+              <c:f>'고1 모의고사'!$B$30:$G$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고1 모의고사'!A31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이시원</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="f59240"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고1 모의고사'!$B$25:$G$25</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>중1 1차
+고1 모의고사</c:v>
+                </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>중2 1차
+고1 모의고사</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>중2 2차
+고1 모의고사</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고1 모의고사'!$B$31:$G$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4391,11 +5608,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="44356650"/>
-        <c:axId val="30514252"/>
+        <c:axId val="4062371"/>
+        <c:axId val="71363443"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="44356650"/>
+        <c:axId val="4062371"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4427,7 +5644,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30514252"/>
+        <c:crossAx val="71363443"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4435,7 +5652,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30514252"/>
+        <c:axId val="71363443"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -4513,7 +5730,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44356650"/>
+        <c:crossAx val="4062371"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -5035,6 +6252,91 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고2 모의고사'!A11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이시원</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="f59240"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고2 모의고사'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중2 3차
+고2 모의고사</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고2 모의고사'!$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>77</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -5043,11 +6345,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="8067198"/>
-        <c:axId val="27172684"/>
+        <c:axId val="78719728"/>
+        <c:axId val="44921377"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8067198"/>
+        <c:axId val="78719728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5079,7 +6381,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27172684"/>
+        <c:crossAx val="44921377"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5087,7 +6389,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27172684"/>
+        <c:axId val="44921377"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5165,7 +6467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8067198"/>
+        <c:crossAx val="78719728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -5267,7 +6569,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A15</c:f>
+              <c:f>'고2 모의고사'!A16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5323,7 +6625,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$14</c:f>
+              <c:f>'고2 모의고사'!$B$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5335,7 +6637,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$15</c:f>
+              <c:f>'고2 모의고사'!$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5352,7 +6654,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A16</c:f>
+              <c:f>'고2 모의고사'!A17</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5408,7 +6710,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$14</c:f>
+              <c:f>'고2 모의고사'!$B$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5420,7 +6722,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$16</c:f>
+              <c:f>'고2 모의고사'!$B$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5437,7 +6739,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A17</c:f>
+              <c:f>'고2 모의고사'!A18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5493,7 +6795,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$14</c:f>
+              <c:f>'고2 모의고사'!$B$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5505,7 +6807,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$17</c:f>
+              <c:f>'고2 모의고사'!$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5522,7 +6824,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A18</c:f>
+              <c:f>'고2 모의고사'!A19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5578,7 +6880,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$14</c:f>
+              <c:f>'고2 모의고사'!$B$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5590,7 +6892,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$18</c:f>
+              <c:f>'고2 모의고사'!$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5607,7 +6909,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A19</c:f>
+              <c:f>'고2 모의고사'!A20</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5663,7 +6965,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$14</c:f>
+              <c:f>'고2 모의고사'!$B$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5675,7 +6977,92 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$19</c:f>
+              <c:f>'고2 모의고사'!$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고2 모의고사'!A21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이시원</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="f59240"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고2 모의고사'!$B$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중2 3차
+고2 모의고사</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고2 모의고사'!$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -5695,11 +7082,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="84178385"/>
-        <c:axId val="97697882"/>
+        <c:axId val="34501327"/>
+        <c:axId val="36036203"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="84178385"/>
+        <c:axId val="34501327"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5731,7 +7118,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97697882"/>
+        <c:crossAx val="36036203"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5739,7 +7126,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97697882"/>
+        <c:axId val="36036203"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -5817,7 +7204,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84178385"/>
+        <c:crossAx val="34501327"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5919,7 +7306,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A24</c:f>
+              <c:f>'고2 모의고사'!A26</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5975,7 +7362,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$23</c:f>
+              <c:f>'고2 모의고사'!$B$25</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5987,7 +7374,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$24</c:f>
+              <c:f>'고2 모의고사'!$B$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6004,7 +7391,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A25</c:f>
+              <c:f>'고2 모의고사'!A27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6060,7 +7447,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$23</c:f>
+              <c:f>'고2 모의고사'!$B$25</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6072,7 +7459,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$25</c:f>
+              <c:f>'고2 모의고사'!$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6089,7 +7476,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A26</c:f>
+              <c:f>'고2 모의고사'!A28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6145,7 +7532,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$23</c:f>
+              <c:f>'고2 모의고사'!$B$25</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6157,7 +7544,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$26</c:f>
+              <c:f>'고2 모의고사'!$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6174,7 +7561,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A27</c:f>
+              <c:f>'고2 모의고사'!A29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6230,7 +7617,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$23</c:f>
+              <c:f>'고2 모의고사'!$B$25</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6242,7 +7629,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$27</c:f>
+              <c:f>'고2 모의고사'!$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6259,7 +7646,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고2 모의고사'!A28</c:f>
+              <c:f>'고2 모의고사'!A30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6315,7 +7702,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고2 모의고사'!$B$23</c:f>
+              <c:f>'고2 모의고사'!$B$25</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6327,12 +7714,97 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고2 모의고사'!$B$28</c:f>
+              <c:f>'고2 모의고사'!$B$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고2 모의고사'!A31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이시원</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="f59240"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고2 모의고사'!$B$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중2 3차
+고2 모의고사</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고2 모의고사'!$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6347,11 +7819,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="97584721"/>
-        <c:axId val="52242780"/>
+        <c:axId val="82168590"/>
+        <c:axId val="58385538"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97584721"/>
+        <c:axId val="82168590"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6383,7 +7855,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52242780"/>
+        <c:crossAx val="58385538"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6391,7 +7863,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="52242780"/>
+        <c:axId val="58385538"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -6469,7 +7941,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97584721"/>
+        <c:crossAx val="82168590"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -6526,16 +7998,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>255960</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>256320</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>72360</xdr:rowOff>
+      <xdr:rowOff>310320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6543,7 +8015,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6814080" y="571680"/>
+        <a:off x="9351720" y="571680"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6556,14 +8028,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>255960</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>256320</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>119520</xdr:rowOff>
     </xdr:to>
@@ -6573,7 +8045,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6814080" y="4095720"/>
+        <a:off x="9351720" y="4095720"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6586,14 +8058,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>255960</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>256320</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>167040</xdr:rowOff>
     </xdr:to>
@@ -6603,7 +8075,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6814080" y="7381800"/>
+        <a:off x="9351720" y="7381800"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6630,7 +8102,7 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>255960</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>72360</xdr:rowOff>
+      <xdr:rowOff>310320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -7033,16 +8505,16 @@
         <v>21</v>
       </c>
       <c r="C5" s="8" t="n">
-        <f aca="false">'고1 모의고사'!E11</f>
-        <v>65.6</v>
+        <f aca="false">'고1 모의고사'!H12</f>
+        <v>65</v>
       </c>
       <c r="D5" s="8" t="n">
-        <f aca="false">'고1 모의고사'!F11</f>
-        <v>80.8</v>
+        <f aca="false">'고1 모의고사'!I12</f>
+        <v>79.1666666666667</v>
       </c>
       <c r="E5" s="9" t="n">
         <f aca="false">D5-C5</f>
-        <v>15.2</v>
+        <v>14.1666666666667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7053,16 +8525,16 @@
         <v>22</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">'고1 모의고사'!E20</f>
+        <f aca="false">'고1 모의고사'!H22</f>
         <v>15.8</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">'고1 모의고사'!F20</f>
-        <v>16.4</v>
+        <f aca="false">'고1 모의고사'!I22</f>
+        <v>16.3333333333333</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">D6-C6</f>
-        <v>0.599999999999998</v>
+        <v>0.533333333333331</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7073,16 +8545,16 @@
         <v>23</v>
       </c>
       <c r="C7" s="8" t="n">
-        <f aca="false">'고1 모의고사'!E29</f>
+        <f aca="false">'고1 모의고사'!H32</f>
         <v>15</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">'고1 모의고사'!F29</f>
-        <v>20.8</v>
+        <f aca="false">'고1 모의고사'!I32</f>
+        <v>20.3333333333333</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">D7-C7</f>
-        <v>5.8</v>
+        <v>5.33333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7093,12 +8565,12 @@
         <v>21</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">'고2 모의고사'!C11</f>
-        <v>82</v>
+        <f aca="false">'고2 모의고사'!C12</f>
+        <v>81.1666666666667</v>
       </c>
       <c r="D8" s="8" t="n">
-        <f aca="false">'고2 모의고사'!D11</f>
-        <v>82</v>
+        <f aca="false">'고2 모의고사'!D12</f>
+        <v>81.1666666666667</v>
       </c>
       <c r="E8" s="9" t="n">
         <f aca="false">D8-C8</f>
@@ -7113,12 +8585,12 @@
         <v>22</v>
       </c>
       <c r="C9" s="8" t="n">
-        <f aca="false">'고2 모의고사'!C20</f>
-        <v>16.8</v>
+        <f aca="false">'고2 모의고사'!C22</f>
+        <v>16.8333333333333</v>
       </c>
       <c r="D9" s="8" t="n">
-        <f aca="false">'고2 모의고사'!D20</f>
-        <v>16.8</v>
+        <f aca="false">'고2 모의고사'!D22</f>
+        <v>16.8333333333333</v>
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">D9-C9</f>
@@ -7133,12 +8605,12 @@
         <v>23</v>
       </c>
       <c r="C10" s="8" t="n">
-        <f aca="false">'고2 모의고사'!C29</f>
-        <v>21</v>
+        <f aca="false">'고2 모의고사'!C32</f>
+        <v>20.6666666666667</v>
       </c>
       <c r="D10" s="8" t="n">
-        <f aca="false">'고2 모의고사'!D29</f>
-        <v>21</v>
+        <f aca="false">'고2 모의고사'!D32</f>
+        <v>20.6666666666667</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">D10-C10</f>
@@ -7161,11 +8633,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7203,540 +8675,815 @@
         <v>33</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>63</v>
       </c>
       <c r="C6" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="G6" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="H6" s="7" t="n">
         <f aca="false">B6</f>
         <v>63</v>
       </c>
-      <c r="F6" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B6:D6)</f>
+      <c r="I6" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B6:G6)</f>
         <v>75</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <f aca="false">F6-E6</f>
+      <c r="J6" s="11" t="n">
+        <f aca="false">I6-H6</f>
         <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>59</v>
       </c>
       <c r="C7" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="G7" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="H7" s="7" t="n">
         <f aca="false">B7</f>
         <v>59</v>
       </c>
-      <c r="F7" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B7:D7)</f>
+      <c r="I7" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B7:G7)</f>
         <v>73</v>
       </c>
-      <c r="G7" s="11" t="n">
-        <f aca="false">F7-E7</f>
+      <c r="J7" s="11" t="n">
+        <f aca="false">I7-H7</f>
         <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>88</v>
       </c>
       <c r="C8" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="G8" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="H8" s="7" t="n">
         <f aca="false">B8</f>
         <v>88</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B8:D8)</f>
+      <c r="I8" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B8:G8)</f>
         <v>100</v>
       </c>
-      <c r="G8" s="11" t="n">
-        <f aca="false">F8-E8</f>
+      <c r="J8" s="11" t="n">
+        <f aca="false">I8-H8</f>
         <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>67</v>
       </c>
       <c r="C9" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="G9" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="H9" s="7" t="n">
         <f aca="false">B9</f>
         <v>67</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B9:D9)</f>
+      <c r="I9" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B9:G9)</f>
         <v>74</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <f aca="false">F9-E9</f>
+      <c r="J9" s="11" t="n">
+        <f aca="false">I9-H9</f>
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B10" s="10" t="n">
         <v>51</v>
       </c>
       <c r="C10" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="G10" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <f aca="false">B10</f>
         <v>51</v>
       </c>
-      <c r="F10" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B10:D10)</f>
+      <c r="I10" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B10:G10)</f>
         <v>82</v>
       </c>
-      <c r="G10" s="11" t="n">
-        <f aca="false">F10-E10</f>
+      <c r="J10" s="11" t="n">
+        <f aca="false">I10-H10</f>
         <v>31</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="13" t="n">
-        <f aca="false">IF(COUNT(B6:B10)=0,"",AVERAGE(B6:B10))</f>
-        <v>65.6</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <f aca="false">IF(COUNT(C6:C10)=0,"",AVERAGE(C6:C10))</f>
-        <v>80.2</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <f aca="false">IF(COUNT(D6:D10)=0,"",AVERAGE(D6:D10))</f>
-        <v>80.8</v>
-      </c>
-      <c r="E11" s="13" t="n">
+      <c r="A11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="H11" s="7" t="n">
         <f aca="false">B11</f>
-        <v>65.6</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B11:D11)</f>
-        <v>80.8</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <f aca="false">F11-E11</f>
-        <v>15.2</v>
+        <v>62</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B11:G11)</f>
+        <v>71</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <f aca="false">I11-H11</f>
+        <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>40</v>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <f aca="false">IF(COUNT(B6:B11)=0,"",AVERAGE(B6:B11))</f>
+        <v>65</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <f aca="false">IF(COUNT(C6:C11)=0,"",AVERAGE(C6:C11))</f>
+        <v>73.1666666666667</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <f aca="false">IF(COUNT(D6:D11)=0,"",AVERAGE(D6:D11))</f>
+        <v>73.8333333333333</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <f aca="false">IF(COUNT(E6:E11)=0,"",AVERAGE(E6:E11))</f>
+        <v>81.3333333333333</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <f aca="false">IF(COUNT(F6:F11)=0,"",AVERAGE(F6:F11))</f>
+        <v>79</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <f aca="false">IF(COUNT(G6:G11)=0,"",AVERAGE(G6:G11))</f>
+        <v>79.1666666666667</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <f aca="false">B12</f>
+        <v>65</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B12:G12)</f>
+        <v>79.1666666666667</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <f aca="false">I12-H12</f>
+        <v>14.1666666666667</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <f aca="false">B15</f>
-        <v>14</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B15:D15)</f>
-        <v>16</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <f aca="false">F15-E15</f>
-        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>17</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C16" s="10"/>
       <c r="D16" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="E16" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" s="7" t="n">
         <f aca="false">B16</f>
-        <v>17</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B16:D16)</f>
-        <v>17</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <f aca="false">F16-E16</f>
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B16:G16)</f>
+        <v>16</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <f aca="false">I16-H16</f>
+        <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="C17" s="10" t="n">
-        <v>17</v>
-      </c>
+      <c r="C17" s="10"/>
       <c r="D17" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H17" s="7" t="n">
         <f aca="false">B17</f>
         <v>17</v>
       </c>
-      <c r="F17" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B17:D17)</f>
+      <c r="I17" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B17:G17)</f>
         <v>17</v>
       </c>
-      <c r="G17" s="11" t="n">
-        <f aca="false">F17-E17</f>
+      <c r="J17" s="11" t="n">
+        <f aca="false">I17-H17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" s="10" t="n">
         <v>17</v>
       </c>
+      <c r="C18" s="10"/>
       <c r="D18" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="E18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H18" s="7" t="n">
         <f aca="false">B18</f>
-        <v>15</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B18:D18)</f>
-        <v>15</v>
-      </c>
-      <c r="G18" s="11" t="n">
-        <f aca="false">F18-E18</f>
+        <v>17</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B18:G18)</f>
+        <v>17</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <f aca="false">I18-H18</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="C19" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="F19" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="G19" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="7" t="n">
         <f aca="false">B19</f>
-        <v>16</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B19:D19)</f>
-        <v>17</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <f aca="false">F19-E19</f>
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B19:G19)</f>
+        <v>15</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <f aca="false">I19-H19</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="13" t="n">
-        <f aca="false">IF(COUNT(B15:B19)=0,"",AVERAGE(B15:B19))</f>
-        <v>15.8</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <f aca="false">IF(COUNT(C15:C19)=0,"",AVERAGE(C15:C19))</f>
-        <v>16.6</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <f aca="false">IF(COUNT(D15:D19)=0,"",AVERAGE(D15:D19))</f>
-        <v>16.4</v>
-      </c>
-      <c r="E20" s="13" t="n">
+      <c r="A20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H20" s="7" t="n">
         <f aca="false">B20</f>
-        <v>15.8</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B20:D20)</f>
-        <v>16.4</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <f aca="false">F20-E20</f>
-        <v>0.599999999999998</v>
+        <v>16</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B20:G20)</f>
+        <v>17</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <f aca="false">I20-H20</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <f aca="false">D21</f>
+        <v>16</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B21:G21)</f>
+        <v>16</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <f aca="false">I21-H21</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>19</v>
+      <c r="A22" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="13" t="n">
+        <f aca="false">IF(COUNT(B16:B21)=0,"",AVERAGE(B16:B21))</f>
+        <v>15.8</v>
+      </c>
+      <c r="C22" s="13" t="str">
+        <f aca="false">IF(COUNT(C16:C21)=0,"",AVERAGE(C16:C21))</f>
+        <v/>
+      </c>
+      <c r="D22" s="13" t="n">
+        <f aca="false">IF(COUNT(D16:D21)=0,"",AVERAGE(D16:D21))</f>
+        <v>16.1666666666667</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <f aca="false">IF(COUNT(E16:E21)=0,"",AVERAGE(E16:E21))</f>
+        <v>16.3333333333333</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <f aca="false">IF(COUNT(F16:F21)=0,"",AVERAGE(F16:F21))</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <f aca="false">IF(COUNT(G16:G21)=0,"",AVERAGE(G16:G21))</f>
+        <v>16.3333333333333</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <f aca="false">B22</f>
+        <v>15.8</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B22:G22)</f>
+        <v>16.3333333333333</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <f aca="false">I22-H22</f>
+        <v>0.533333333333331</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <f aca="false">B24</f>
-        <v>16</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B24:D24)</f>
-        <v>18</v>
-      </c>
-      <c r="G24" s="11" t="n">
-        <f aca="false">F24-E24</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="H25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <f aca="false">B25</f>
-        <v>11</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B25:D25)</f>
-        <v>17</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <f aca="false">F25-E25</f>
-        <v>6</v>
+      <c r="I25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>23</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C26" s="10"/>
       <c r="D26" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="E26" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H26" s="7" t="n">
         <f aca="false">B26</f>
-        <v>23</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B26:D26)</f>
-        <v>28</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <f aca="false">F26-E26</f>
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B26:G26)</f>
+        <v>18</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <f aca="false">I26-H26</f>
+        <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="G27" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="C27" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E27" s="7" t="n">
+      <c r="H27" s="7" t="n">
         <f aca="false">B27</f>
+        <v>11</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B27:G27)</f>
         <v>17</v>
       </c>
-      <c r="F27" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B27:D27)</f>
-        <v>20</v>
-      </c>
-      <c r="G27" s="11" t="n">
-        <f aca="false">F27-E27</f>
-        <v>3</v>
+      <c r="J27" s="11" t="n">
+        <f aca="false">I27-H27</f>
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>18</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C28" s="10"/>
       <c r="D28" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="E28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H28" s="7" t="n">
         <f aca="false">B28</f>
-        <v>8</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B28:D28)</f>
-        <v>21</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <f aca="false">F28-E28</f>
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B28:G28)</f>
+        <v>28</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <f aca="false">I28-H28</f>
+        <v>5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="13" t="n">
-        <f aca="false">IF(COUNT(B24:B28)=0,"",AVERAGE(B24:B28))</f>
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <f aca="false">B29</f>
+        <v>17</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B29:G29)</f>
+        <v>20</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <f aca="false">I29-H29</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <f aca="false">B30</f>
+        <v>8</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B30:G30)</f>
+        <v>21</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <f aca="false">I30-H30</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <f aca="false">D31</f>
+        <v>16</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B31:G31)</f>
+        <v>18</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <f aca="false">I31-H31</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="13" t="n">
+        <f aca="false">IF(COUNT(B26:B31)=0,"",AVERAGE(B26:B31))</f>
         <v>15</v>
       </c>
-      <c r="C29" s="13" t="n">
-        <f aca="false">IF(COUNT(C24:C28)=0,"",AVERAGE(C24:C28))</f>
-        <v>20.8</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <f aca="false">IF(COUNT(D24:D28)=0,"",AVERAGE(D24:D28))</f>
-        <v>20.8</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <f aca="false">B29</f>
+      <c r="C32" s="13" t="str">
+        <f aca="false">IF(COUNT(C26:C31)=0,"",AVERAGE(C26:C31))</f>
+        <v/>
+      </c>
+      <c r="D32" s="13" t="n">
+        <f aca="false">IF(COUNT(D26:D31)=0,"",AVERAGE(D26:D31))</f>
+        <v>18</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <f aca="false">IF(COUNT(E26:E31)=0,"",AVERAGE(E26:E31))</f>
+        <v>21</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <f aca="false">IF(COUNT(F26:F31)=0,"",AVERAGE(F26:F31))</f>
+        <v>20.1666666666667</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <f aca="false">IF(COUNT(G26:G31)=0,"",AVERAGE(G26:G31))</f>
+        <v>20.3333333333333</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <f aca="false">B32</f>
         <v>15</v>
       </c>
-      <c r="F29" s="13" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B29:D29)</f>
-        <v>20.8</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <f aca="false">F29-E29</f>
-        <v>5.8</v>
+      <c r="I32" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B32:G32)</f>
+        <v>20.3333333333333</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <f aca="false">I32-H32</f>
+        <v>5.33333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7747,7 +9494,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -7756,7 +9504,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -7765,12 +9513,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7783,13 +9531,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>19</v>
@@ -7797,7 +9545,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>77</v>
@@ -7817,7 +9565,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>76</v>
@@ -7837,7 +9585,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>95</v>
@@ -7857,7 +9605,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>82</v>
@@ -7877,7 +9625,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B10" s="10" t="n">
         <v>80</v>
@@ -7896,82 +9644,82 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="13" t="n">
-        <f aca="false">IF(COUNT(B6:B10)=0,"",AVERAGE(B6:B10))</f>
-        <v>82</v>
-      </c>
-      <c r="C11" s="13" t="n">
+      <c r="A11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <f aca="false">B11</f>
-        <v>82</v>
-      </c>
-      <c r="D11" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="D11" s="7" t="n">
         <f aca="false">LOOKUP(9.99E+307,B11:B11)</f>
-        <v>82</v>
-      </c>
-      <c r="E11" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <f aca="false">D11-C11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>40</v>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <f aca="false">IF(COUNT(B6:B11)=0,"",AVERAGE(B6:B11))</f>
+        <v>81.1666666666667</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <f aca="false">B12</f>
+        <v>81.1666666666667</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B12:B12)</f>
+        <v>81.1666666666667</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <f aca="false">D12-C12</f>
+        <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="B15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <f aca="false">B15</f>
-        <v>17</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B15:B15)</f>
-        <v>17</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <f aca="false">D15-C15</f>
-        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">B16</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7" t="n">
         <f aca="false">LOOKUP(9.99E+307,B16:B16)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16" s="11" t="n">
         <f aca="false">D16-C16</f>
@@ -7980,18 +9728,18 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
         <f aca="false">B17</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="7" t="n">
         <f aca="false">LOOKUP(9.99E+307,B17:B17)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" s="11" t="n">
         <f aca="false">D17-C17</f>
@@ -8000,7 +9748,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>17</v>
@@ -8020,7 +9768,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>17</v>
@@ -8039,102 +9787,102 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="13" t="n">
-        <f aca="false">IF(COUNT(B15:B19)=0,"",AVERAGE(B15:B19))</f>
-        <v>16.8</v>
-      </c>
-      <c r="C20" s="13" t="n">
+      <c r="A20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" s="7" t="n">
         <f aca="false">B20</f>
-        <v>16.8</v>
-      </c>
-      <c r="D20" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="n">
         <f aca="false">LOOKUP(9.99E+307,B20:B20)</f>
-        <v>16.8</v>
-      </c>
-      <c r="E20" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E20" s="11" t="n">
         <f aca="false">D20-C20</f>
         <v>0</v>
       </c>
     </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <f aca="false">B21</f>
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B21:B21)</f>
+        <v>17</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <f aca="false">D21-C21</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>19</v>
+      <c r="A22" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="13" t="n">
+        <f aca="false">IF(COUNT(B16:B21)=0,"",AVERAGE(B16:B21))</f>
+        <v>16.8333333333333</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <f aca="false">B22</f>
+        <v>16.8333333333333</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B22:B22)</f>
+        <v>16.8333333333333</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <f aca="false">D22-C22</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="10" t="n">
+      <c r="A24" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <f aca="false">B24</f>
-        <v>19</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B24:B24)</f>
-        <v>19</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <f aca="false">D24-C24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <f aca="false">B25</f>
-        <v>19</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B25:B25)</f>
-        <v>19</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <f aca="false">D25-C25</f>
-        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26" s="10" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C26" s="7" t="n">
         <f aca="false">B26</f>
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D26" s="7" t="n">
         <f aca="false">LOOKUP(9.99E+307,B26:B26)</f>
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E26" s="11" t="n">
         <f aca="false">D26-C26</f>
@@ -8143,18 +9891,18 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C27" s="7" t="n">
         <f aca="false">B27</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D27" s="7" t="n">
         <f aca="false">LOOKUP(9.99E+307,B27:B27)</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E27" s="11" t="n">
         <f aca="false">D27-C27</f>
@@ -8163,18 +9911,18 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="10" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C28" s="7" t="n">
         <f aca="false">B28</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D28" s="7" t="n">
         <f aca="false">LOOKUP(9.99E+307,B28:B28)</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E28" s="11" t="n">
         <f aca="false">D28-C28</f>
@@ -8182,23 +9930,83 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="13" t="n">
-        <f aca="false">IF(COUNT(B24:B28)=0,"",AVERAGE(B24:B28))</f>
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="7" t="n">
         <f aca="false">B29</f>
         <v>21</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="7" t="n">
         <f aca="false">LOOKUP(9.99E+307,B29:B29)</f>
         <v>21</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="11" t="n">
         <f aca="false">D29-C29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <f aca="false">B30</f>
+        <v>20</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B30:B30)</f>
+        <v>20</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <f aca="false">D30-C30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <f aca="false">B31</f>
+        <v>19</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B31:B31)</f>
+        <v>19</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <f aca="false">D31-C31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="13" t="n">
+        <f aca="false">IF(COUNT(B26:B31)=0,"",AVERAGE(B26:B31))</f>
+        <v>20.6666666666667</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <f aca="false">B32</f>
+        <v>20.6666666666667</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B32:B32)</f>
+        <v>20.6666666666667</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <f aca="false">D32-C32</f>
         <v>0</v>
       </c>
     </row>

--- a/output/isabel-cohorts/이서연반_시험수준별_성적.xlsx
+++ b/output/isabel-cohorts/이서연반_시험수준별_성적.xlsx
@@ -3756,11 +3756,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="32900627"/>
-        <c:axId val="21361670"/>
+        <c:axId val="94094777"/>
+        <c:axId val="25766089"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="32900627"/>
+        <c:axId val="94094777"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3792,7 +3792,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21361670"/>
+        <c:crossAx val="25766089"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3800,7 +3800,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21361670"/>
+        <c:axId val="25766089"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3878,7 +3878,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32900627"/>
+        <c:crossAx val="94094777"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -4682,11 +4682,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="42062392"/>
-        <c:axId val="50354999"/>
+        <c:axId val="12194273"/>
+        <c:axId val="46152682"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="42062392"/>
+        <c:axId val="12194273"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4718,7 +4718,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50354999"/>
+        <c:crossAx val="46152682"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4726,7 +4726,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50354999"/>
+        <c:axId val="46152682"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -4804,7 +4804,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42062392"/>
+        <c:crossAx val="12194273"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5608,11 +5608,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="4062371"/>
-        <c:axId val="71363443"/>
+        <c:axId val="85079007"/>
+        <c:axId val="43457598"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="4062371"/>
+        <c:axId val="85079007"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5644,7 +5644,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71363443"/>
+        <c:crossAx val="43457598"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5652,7 +5652,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71363443"/>
+        <c:axId val="43457598"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -5730,7 +5730,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4062371"/>
+        <c:crossAx val="85079007"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -6345,11 +6345,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="78719728"/>
-        <c:axId val="44921377"/>
+        <c:axId val="10438701"/>
+        <c:axId val="61362784"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="78719728"/>
+        <c:axId val="10438701"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6381,7 +6381,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44921377"/>
+        <c:crossAx val="61362784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6389,7 +6389,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44921377"/>
+        <c:axId val="61362784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6467,7 +6467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78719728"/>
+        <c:crossAx val="10438701"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -7082,11 +7082,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="34501327"/>
-        <c:axId val="36036203"/>
+        <c:axId val="57745002"/>
+        <c:axId val="85275129"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="34501327"/>
+        <c:axId val="57745002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7118,7 +7118,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36036203"/>
+        <c:crossAx val="85275129"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7126,7 +7126,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36036203"/>
+        <c:axId val="85275129"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -7204,7 +7204,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34501327"/>
+        <c:crossAx val="57745002"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -7819,11 +7819,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="82168590"/>
-        <c:axId val="58385538"/>
+        <c:axId val="79990972"/>
+        <c:axId val="54455195"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="82168590"/>
+        <c:axId val="79990972"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7855,7 +7855,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58385538"/>
+        <c:crossAx val="54455195"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7863,7 +7863,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58385538"/>
+        <c:axId val="54455195"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -7941,7 +7941,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82168590"/>
+        <c:crossAx val="79990972"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>

--- a/output/isabel-cohorts/이서연반_시험수준별_성적.xlsx
+++ b/output/isabel-cohorts/이서연반_시험수준별_성적.xlsx
@@ -3756,11 +3756,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="94094777"/>
-        <c:axId val="25766089"/>
+        <c:axId val="94713447"/>
+        <c:axId val="9080399"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="94094777"/>
+        <c:axId val="94713447"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3792,7 +3792,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25766089"/>
+        <c:crossAx val="9080399"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3800,7 +3800,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25766089"/>
+        <c:axId val="9080399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -3878,7 +3878,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94094777"/>
+        <c:crossAx val="94713447"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -4682,11 +4682,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="12194273"/>
-        <c:axId val="46152682"/>
+        <c:axId val="61262857"/>
+        <c:axId val="42836740"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="12194273"/>
+        <c:axId val="61262857"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4718,7 +4718,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46152682"/>
+        <c:crossAx val="42836740"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4726,7 +4726,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46152682"/>
+        <c:axId val="42836740"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -4804,7 +4804,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12194273"/>
+        <c:crossAx val="61262857"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5608,11 +5608,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="85079007"/>
-        <c:axId val="43457598"/>
+        <c:axId val="51694380"/>
+        <c:axId val="93652359"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="85079007"/>
+        <c:axId val="51694380"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5644,7 +5644,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43457598"/>
+        <c:crossAx val="93652359"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5652,7 +5652,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43457598"/>
+        <c:axId val="93652359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -5730,7 +5730,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85079007"/>
+        <c:crossAx val="51694380"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -6345,11 +6345,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="10438701"/>
-        <c:axId val="61362784"/>
+        <c:axId val="57627378"/>
+        <c:axId val="93366893"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10438701"/>
+        <c:axId val="57627378"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6381,7 +6381,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61362784"/>
+        <c:crossAx val="93366893"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6389,7 +6389,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61362784"/>
+        <c:axId val="93366893"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6467,7 +6467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10438701"/>
+        <c:crossAx val="57627378"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -7082,11 +7082,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="57745002"/>
-        <c:axId val="85275129"/>
+        <c:axId val="91207537"/>
+        <c:axId val="54688149"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="57745002"/>
+        <c:axId val="91207537"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7118,7 +7118,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85275129"/>
+        <c:crossAx val="54688149"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7126,7 +7126,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85275129"/>
+        <c:axId val="54688149"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -7204,7 +7204,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57745002"/>
+        <c:crossAx val="91207537"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -7819,11 +7819,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="79990972"/>
-        <c:axId val="54455195"/>
+        <c:axId val="30377201"/>
+        <c:axId val="40521071"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="79990972"/>
+        <c:axId val="30377201"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7855,7 +7855,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54455195"/>
+        <c:crossAx val="40521071"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7863,7 +7863,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54455195"/>
+        <c:axId val="40521071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -7941,7 +7941,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79990972"/>
+        <c:crossAx val="30377201"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
